--- a/Python/Strings Comparer/ExcelData/merchant-app-string.xlsx
+++ b/Python/Strings Comparer/ExcelData/merchant-app-string.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="619">
   <si>
     <t>Key</t>
   </si>
@@ -488,6 +488,1386 @@
   </si>
   <si>
     <t>Driver reached near the location</t>
+  </si>
+  <si>
+    <t>button_chat</t>
+  </si>
+  <si>
+    <t>Chat</t>
+  </si>
+  <si>
+    <t>button_add_new_customization_sd</t>
+  </si>
+  <si>
+    <t>Add new customization</t>
+  </si>
+  <si>
+    <t>button_add_sd</t>
+  </si>
+  <si>
+    <t>Add {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>button_add_to_cart_qd</t>
+  </si>
+  <si>
+    <t>Add To Cart</t>
+  </si>
+  <si>
+    <t>button_complete_order</t>
+  </si>
+  <si>
+    <t>Complete Order</t>
+  </si>
+  <si>
+    <t>button_customize_sd</t>
+  </si>
+  <si>
+    <t>Customise</t>
+  </si>
+  <si>
+    <t>button_delivery_sd</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>button_dropoff_onsite_ss</t>
+  </si>
+  <si>
+    <t>Drop at my location after service</t>
+  </si>
+  <si>
+    <t>button_on_site_service_ss</t>
+  </si>
+  <si>
+    <t>On-Site</t>
+  </si>
+  <si>
+    <t>button_online_service_ss</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>button_pickup_onsite_ss</t>
+  </si>
+  <si>
+    <t>Pick at my location</t>
+  </si>
+  <si>
+    <t>button_pickup_sd</t>
+  </si>
+  <si>
+    <t>Pickup</t>
+  </si>
+  <si>
+    <t>button_pickup_service_ss</t>
+  </si>
+  <si>
+    <t>At Home</t>
+  </si>
+  <si>
+    <t>button_place_order_qd</t>
+  </si>
+  <si>
+    <t>Place Order</t>
+  </si>
+  <si>
+    <t>button_purchase_subscription</t>
+  </si>
+  <si>
+    <t>Purchase Subscription</t>
+  </si>
+  <si>
+    <t>button_renew</t>
+  </si>
+  <si>
+    <t>button_save_slot</t>
+  </si>
+  <si>
+    <t>Save Slot</t>
+  </si>
+  <si>
+    <t>button_update</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>button_upgrade</t>
+  </si>
+  <si>
+    <t>button_variant_options_qd</t>
+  </si>
+  <si>
+    <t>{{_VALUE}} Options</t>
+  </si>
+  <si>
+    <t>button_view_all_qd</t>
+  </si>
+  <si>
+    <t>View All</t>
+  </si>
+  <si>
+    <t>button_view_benefits</t>
+  </si>
+  <si>
+    <t>View Benefits</t>
+  </si>
+  <si>
+    <t>button_view_cancellation_policy</t>
+  </si>
+  <si>
+    <t>View Cancellation Policy</t>
+  </si>
+  <si>
+    <t>button_view_cart_qd</t>
+  </si>
+  <si>
+    <t>View Cart</t>
+  </si>
+  <si>
+    <t>button_view_referral_policy</t>
+  </si>
+  <si>
+    <t>View Referral Policy</t>
+  </si>
+  <si>
+    <t>button_yes_sure</t>
+  </si>
+  <si>
+    <t>Yes, Sure</t>
+  </si>
+  <si>
+    <t>description_accepted</t>
+  </si>
+  <si>
+    <t>description_action_subscription</t>
+  </si>
+  <si>
+    <t>Are you sure you want to proceed?</t>
+  </si>
+  <si>
+    <t>description_active</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>description_add_more_sd</t>
+  </si>
+  <si>
+    <t>Add More</t>
+  </si>
+  <si>
+    <t>description_additional_info</t>
+  </si>
+  <si>
+    <t>Additional info</t>
+  </si>
+  <si>
+    <t>description_allow_cooking_time</t>
+  </si>
+  <si>
+    <t>Allow Cooking Time on Accept</t>
+  </si>
+  <si>
+    <t>description_applied_on</t>
+  </si>
+  <si>
+    <t>Applied On ({{_VALUE}})</t>
+  </si>
+  <si>
+    <t>description_apply_cancellation_charge_from_status</t>
+  </si>
+  <si>
+    <t>Apply Cancellation Charge From Status</t>
+  </si>
+  <si>
+    <t>description_apply_on_full_day</t>
+  </si>
+  <si>
+    <t>Apply on full day?</t>
+  </si>
+  <si>
+    <t>description_are_you_sure_remove_item</t>
+  </si>
+  <si>
+    <t>Are you sure you want to remove?</t>
+  </si>
+  <si>
+    <t>description_assign_deliveryman_on_accept</t>
+  </si>
+  <si>
+    <t>Assign Deliveryman on Accept</t>
+  </si>
+  <si>
+    <t>description_auto_accept</t>
+  </si>
+  <si>
+    <t>Auto Accept</t>
+  </si>
+  <si>
+    <t>description_bank_pending</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>description_bank_processing</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>description_bank_verified</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>description_billing_details</t>
+  </si>
+  <si>
+    <t>BILLING DETAILS</t>
+  </si>
+  <si>
+    <t>description_billing_details_qd</t>
+  </si>
+  <si>
+    <t>description_booking_type</t>
+  </si>
+  <si>
+    <t>Booking Type</t>
+  </si>
+  <si>
+    <t>description_cancel_booking</t>
+  </si>
+  <si>
+    <t>Cancel Booking</t>
+  </si>
+  <si>
+    <t>description_cancel_up_to_status</t>
+  </si>
+  <si>
+    <t>Cancel Up to Status</t>
+  </si>
+  <si>
+    <t>description_cancellation_fees</t>
+  </si>
+  <si>
+    <t>Cancellation Fees</t>
+  </si>
+  <si>
+    <t>description_cancellation_setting</t>
+  </si>
+  <si>
+    <t>Cancellation Setting</t>
+  </si>
+  <si>
+    <t>description_check_day_setting</t>
+  </si>
+  <si>
+    <t>Check Day Setting</t>
+  </si>
+  <si>
+    <t>description_clear_qd</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>description_closed_sd</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>description_copied</t>
+  </si>
+  <si>
+    <t>Copied!</t>
+  </si>
+  <si>
+    <t>description_courier</t>
+  </si>
+  <si>
+    <t>Courier</t>
+  </si>
+  <si>
+    <t>description_courier_group_tag</t>
+  </si>
+  <si>
+    <t>Courier Group</t>
+  </si>
+  <si>
+    <t>description_customer_pickup_alert</t>
+  </si>
+  <si>
+    <t>Can you confirm that the customer has picked up your order?</t>
+  </si>
+  <si>
+    <t>description_day_setting</t>
+  </si>
+  <si>
+    <t>Day Setting</t>
+  </si>
+  <si>
+    <t>description_deliver_to_qd</t>
+  </si>
+  <si>
+    <t>Deliver To:</t>
+  </si>
+  <si>
+    <t>description_delivery_in_min_qd</t>
+  </si>
+  <si>
+    <t>Delivery in {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_delivery_schedule_settings</t>
+  </si>
+  <si>
+    <t>Delivery Schedule Setting</t>
+  </si>
+  <si>
+    <t>description_delivery_setting</t>
+  </si>
+  <si>
+    <t>Delivery Setting</t>
+  </si>
+  <si>
+    <t>description_delivery_slot</t>
+  </si>
+  <si>
+    <t>Delivery Slot</t>
+  </si>
+  <si>
+    <t>description_description_qd</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>description_dimension</t>
+  </si>
+  <si>
+    <t>Dimension - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_discounts_and_offers</t>
+  </si>
+  <si>
+    <t>Discounts and Offers</t>
+  </si>
+  <si>
+    <t>description_doc_expired</t>
+  </si>
+  <si>
+    <t>Expired</t>
+  </si>
+  <si>
+    <t>description_drop_off_items</t>
+  </si>
+  <si>
+    <t>Drop off items</t>
+  </si>
+  <si>
+    <t>description_dropoff_onsite_tag_ss</t>
+  </si>
+  <si>
+    <t>descriptionDropOffOnsiteTagSS</t>
+  </si>
+  <si>
+    <t>description_earning_completed_booking</t>
+  </si>
+  <si>
+    <t>Completed Booking</t>
+  </si>
+  <si>
+    <t>description_earning_penalty</t>
+  </si>
+  <si>
+    <t>Penalty</t>
+  </si>
+  <si>
+    <t>description_earning_reward_points</t>
+  </si>
+  <si>
+    <t>Reward Points</t>
+  </si>
+  <si>
+    <t>description_earning_total_booking</t>
+  </si>
+  <si>
+    <t>Total Booking</t>
+  </si>
+  <si>
+    <t>description_earning_total_cash_revenue</t>
+  </si>
+  <si>
+    <t>Total Cash Revenue</t>
+  </si>
+  <si>
+    <t>description_earning_total_revenue</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>description_eate_awful</t>
+  </si>
+  <si>
+    <t>Awful</t>
+  </si>
+  <si>
+    <t>description_eate_excellent</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>description_eate_good</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>description_eate_sad</t>
+  </si>
+  <si>
+    <t>Sad</t>
+  </si>
+  <si>
+    <t>description_eate_veryGood</t>
+  </si>
+  <si>
+    <t>Very Good</t>
+  </si>
+  <si>
+    <t>description_expired</t>
+  </si>
+  <si>
+    <t>Expired!</t>
+  </si>
+  <si>
+    <t>description_expires_soon</t>
+  </si>
+  <si>
+    <t>Expires soon!</t>
+  </si>
+  <si>
+    <t>description_explore_all_products_qd</t>
+  </si>
+  <si>
+    <t>Explore all products</t>
+  </si>
+  <si>
+    <t>description_fees_applied_status</t>
+  </si>
+  <si>
+    <t>Fees Applied Status</t>
+  </si>
+  <si>
+    <t>description_free_cancellation_time</t>
+  </si>
+  <si>
+    <t>Free Cancellation Time</t>
+  </si>
+  <si>
+    <t>description_free_trial</t>
+  </si>
+  <si>
+    <t>Free Trial</t>
+  </si>
+  <si>
+    <t>description_hyperpay</t>
+  </si>
+  <si>
+    <t>Hyperpay</t>
+  </si>
+  <si>
+    <t>description_images</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>description_inclusive_of_all_taxes_qd</t>
+  </si>
+  <si>
+    <t>inclusive of all taxes</t>
+  </si>
+  <si>
+    <t>description_instant_delivery</t>
+  </si>
+  <si>
+    <t>Delivery at my location</t>
+  </si>
+  <si>
+    <t>description_inter_city_courier</t>
+  </si>
+  <si>
+    <t>Inter City Courier</t>
+  </si>
+  <si>
+    <t>description_intra_city_courier</t>
+  </si>
+  <si>
+    <t>Intra City Courier</t>
+  </si>
+  <si>
+    <t>description_invite_your_friend_and_earn_money</t>
+  </si>
+  <si>
+    <t>Invite Your Friend and \nEarn Money</t>
+  </si>
+  <si>
+    <t>description_invoice_traffic_time</t>
+  </si>
+  <si>
+    <t>Traffic Time</t>
+  </si>
+  <si>
+    <t>description_is_active</t>
+  </si>
+  <si>
+    <t>Is Active</t>
+  </si>
+  <si>
+    <t>description_item_out_of_stock_qd</t>
+  </si>
+  <si>
+    <t>Item out of stock</t>
+  </si>
+  <si>
+    <t>description_item_qd</t>
+  </si>
+  <si>
+    <t>{{_UNIT_VALUE}} Item</t>
+  </si>
+  <si>
+    <t>description_items_qd</t>
+  </si>
+  <si>
+    <t>{{_UNIT_VALUE}} Items</t>
+  </si>
+  <si>
+    <t>description_key_features_qd</t>
+  </si>
+  <si>
+    <t>KEY FEATURES</t>
+  </si>
+  <si>
+    <t>description_life_time</t>
+  </si>
+  <si>
+    <t>Life Time</t>
+  </si>
+  <si>
+    <t>description_max_preparation_time</t>
+  </si>
+  <si>
+    <t>Max. Preparation Time</t>
+  </si>
+  <si>
+    <t>description_mercado_pago</t>
+  </si>
+  <si>
+    <t>Mercado Pago</t>
+  </si>
+  <si>
+    <t>description_merchant_mismatch_alert_message_sd</t>
+  </si>
+  <si>
+    <t>You are about to add an item from a different merchant to your cart. This will remove the items from your current cart. Do you want to continue?</t>
+  </si>
+  <si>
+    <t>description_min</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>description_min_order_price</t>
+  </si>
+  <si>
+    <t>Min Order Price</t>
+  </si>
+  <si>
+    <t>description_min_preparation_time</t>
+  </si>
+  <si>
+    <t>Min. Preparation Time</t>
+  </si>
+  <si>
+    <t>description_movers_and_packers</t>
+  </si>
+  <si>
+    <t>Movers</t>
+  </si>
+  <si>
+    <t>description_mpesa</t>
+  </si>
+  <si>
+    <t>Mpesa</t>
+  </si>
+  <si>
+    <t>description_name_courier</t>
+  </si>
+  <si>
+    <t>Name: {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_nestpay</t>
+  </si>
+  <si>
+    <t>NestPay</t>
+  </si>
+  <si>
+    <t>description_no_data_found</t>
+  </si>
+  <si>
+    <t>No Data Found</t>
+  </si>
+  <si>
+    <t>description_off_qd</t>
+  </si>
+  <si>
+    <t>{{_VALUE}}% OFF</t>
+  </si>
+  <si>
+    <t>description_online_service</t>
+  </si>
+  <si>
+    <t>Online Service</t>
+  </si>
+  <si>
+    <t>description_online_service_ss</t>
+  </si>
+  <si>
+    <t>description_only_delivery_location_sd</t>
+  </si>
+  <si>
+    <t>Only Delivery available in this location</t>
+  </si>
+  <si>
+    <t>description_only_online_service_ss</t>
+  </si>
+  <si>
+    <t>This location offers only online services</t>
+  </si>
+  <si>
+    <t>description_only_onsite_service_ss</t>
+  </si>
+  <si>
+    <t>This location offers only on-site service</t>
+  </si>
+  <si>
+    <t>description_only_pickup_location_sd</t>
+  </si>
+  <si>
+    <t>Only Pickup available in this location</t>
+  </si>
+  <si>
+    <t>description_only_pickup_service_ss</t>
+  </si>
+  <si>
+    <t>This location only offers service at home</t>
+  </si>
+  <si>
+    <t>description_onsite_service</t>
+  </si>
+  <si>
+    <t>On Site Service</t>
+  </si>
+  <si>
+    <t>description_order_for_qd</t>
+  </si>
+  <si>
+    <t>Ordered For</t>
+  </si>
+  <si>
+    <t>description_order_setting</t>
+  </si>
+  <si>
+    <t>Order Setting</t>
+  </si>
+  <si>
+    <t>description_ordered_for</t>
+  </si>
+  <si>
+    <t>description_orders_count</t>
+  </si>
+  <si>
+    <t>Orders</t>
+  </si>
+  <si>
+    <t>description_otp</t>
+  </si>
+  <si>
+    <t>OTP {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_out_of_stock_qd</t>
+  </si>
+  <si>
+    <t>Out of Stock</t>
+  </si>
+  <si>
+    <t>description_pago</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>description_payment_pending</t>
+  </si>
+  <si>
+    <t>Payment is pending!</t>
+  </si>
+  <si>
+    <t>description_paymob</t>
+  </si>
+  <si>
+    <t>Paymob</t>
+  </si>
+  <si>
+    <t>description_payu</t>
+  </si>
+  <si>
+    <t>PayU</t>
+  </si>
+  <si>
+    <t>description_pending</t>
+  </si>
+  <si>
+    <t>description_phone_courier</t>
+  </si>
+  <si>
+    <t>Phone: {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_picker_setting</t>
+  </si>
+  <si>
+    <t>Picker Setting</t>
+  </si>
+  <si>
+    <t>description_pickup_from_sd</t>
+  </si>
+  <si>
+    <t>Pickup from :</t>
+  </si>
+  <si>
+    <t>description_pickup_items</t>
+  </si>
+  <si>
+    <t>Pickup items</t>
+  </si>
+  <si>
+    <t>description_pickup_onsite_tag_ss</t>
+  </si>
+  <si>
+    <t>description_plan_basic</t>
+  </si>
+  <si>
+    <t>BASIC</t>
+  </si>
+  <si>
+    <t>description_plan_premium</t>
+  </si>
+  <si>
+    <t>PREMIUM</t>
+  </si>
+  <si>
+    <t>description_plan_professional</t>
+  </si>
+  <si>
+    <t>PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>description_plan_standard</t>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>description_preparation_time</t>
+  </si>
+  <si>
+    <t>Preparation Time (in minutes)</t>
+  </si>
+  <si>
+    <t>description_price_rating</t>
+  </si>
+  <si>
+    <t>Price Rating</t>
+  </si>
+  <si>
+    <t>description_profit</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>description_qicard</t>
+  </si>
+  <si>
+    <t>QiCard</t>
+  </si>
+  <si>
+    <t>description_ready_for_pickup_alert</t>
+  </si>
+  <si>
+    <t>Can you confirm that your order is ready for pickup?</t>
+  </si>
+  <si>
+    <t>description_recent_search</t>
+  </si>
+  <si>
+    <t>Recent Search</t>
+  </si>
+  <si>
+    <t>description_referral_list</t>
+  </si>
+  <si>
+    <t>Referral List</t>
+  </si>
+  <si>
+    <t>description_rejected</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>description_reopen_at_sd</t>
+  </si>
+  <si>
+    <t>REOPENS AT {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_repeat_last_customization_sd</t>
+  </si>
+  <si>
+    <t>Repeat last customization?</t>
+  </si>
+  <si>
+    <t>description_scheduled_time</t>
+  </si>
+  <si>
+    <t>Scheduled Delivery: {{_SCHEDULED_TIME}}</t>
+  </si>
+  <si>
+    <t>description_select_any_one_sd</t>
+  </si>
+  <si>
+    <t>Select any 1</t>
+  </si>
+  <si>
+    <t>description_select_end_time</t>
+  </si>
+  <si>
+    <t>Select end time</t>
+  </si>
+  <si>
+    <t>description_select_minimum_and_upto_sd</t>
+  </si>
+  <si>
+    <t>Select minimun {{_VALUE}} and up to {{_VALUE1}}</t>
+  </si>
+  <si>
+    <t>description_select_start_time</t>
+  </si>
+  <si>
+    <t>Select start time</t>
+  </si>
+  <si>
+    <t>description_select_unit_qd</t>
+  </si>
+  <si>
+    <t>Select Unit</t>
+  </si>
+  <si>
+    <t>description_select_up_to_sd</t>
+  </si>
+  <si>
+    <t>Select up to {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_service</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>description_service_address_ss</t>
+  </si>
+  <si>
+    <t>Service Address</t>
+  </si>
+  <si>
+    <t>description_service_at_home</t>
+  </si>
+  <si>
+    <t>Service At Home</t>
+  </si>
+  <si>
+    <t>description_service_setting</t>
+  </si>
+  <si>
+    <t>Service Setting</t>
+  </si>
+  <si>
+    <t>description_start_preparing_alert</t>
+  </si>
+  <si>
+    <t>Are you sure that you are going to start preparing the order?</t>
+  </si>
+  <si>
+    <t>description_subscription</t>
+  </si>
+  <si>
+    <t>description_tags</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>description_tip_deliveryman_qd</t>
+  </si>
+  <si>
+    <t>TIP YOUR DELIVERYMAN</t>
+  </si>
+  <si>
+    <t>description_uni_value_per_unit</t>
+  </si>
+  <si>
+    <t>{{_UNIT_VALUE}} / {{_UNIT}}</t>
+  </si>
+  <si>
+    <t>description_unit_qd</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>description_update_business_off</t>
+  </si>
+  <si>
+    <t>Do you want to turn off the business ?</t>
+  </si>
+  <si>
+    <t>description_update_business_on</t>
+  </si>
+  <si>
+    <t>Do you want to turn on the business ?</t>
+  </si>
+  <si>
+    <t>description_uploaded</t>
+  </si>
+  <si>
+    <t>Uploaded</t>
+  </si>
+  <si>
+    <t>description_user_approval_edit_item</t>
+  </si>
+  <si>
+    <t>User approval is pending for edit item</t>
+  </si>
+  <si>
+    <t>description_user_schedule_buffer</t>
+  </si>
+  <si>
+    <t>User Schedule Buffer</t>
+  </si>
+  <si>
+    <t>description_uses_own_delivery_fee</t>
+  </si>
+  <si>
+    <t>Uses Own Delivery Fee</t>
+  </si>
+  <si>
+    <t>description_uses_own_delivery_man</t>
+  </si>
+  <si>
+    <t>Uses Own Delivery Man</t>
+  </si>
+  <si>
+    <t>description_value_days</t>
+  </si>
+  <si>
+    <t>{{_VALUE}} days</t>
+  </si>
+  <si>
+    <t>description_value_free_trial</t>
+  </si>
+  <si>
+    <t>{{_VALUE}} free trial days</t>
+  </si>
+  <si>
+    <t>description_value_of_parcel</t>
+  </si>
+  <si>
+    <t>Value of parcel - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_weight</t>
+  </si>
+  <si>
+    <t>Weight - {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_were_house</t>
+  </si>
+  <si>
+    <t>Were house</t>
+  </si>
+  <si>
+    <t>description_you_saved</t>
+  </si>
+  <si>
+    <t>You Saved {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>description_your_plan_expires_in_days</t>
+  </si>
+  <si>
+    <t>Your plan expires in {{_VALUE}} days!</t>
+  </si>
+  <si>
+    <t>description_zaincash</t>
+  </si>
+  <si>
+    <t>ZainCash</t>
+  </si>
+  <si>
+    <t>error_discount_amount_should_not_greater_than_price</t>
+  </si>
+  <si>
+    <t>Discount amount should not be greater than price</t>
+  </si>
+  <si>
+    <t>error_only_units_allowed_for_product_sd</t>
+  </si>
+  <si>
+    <t>Only {{_VALUE}} units are allowed for this product</t>
+  </si>
+  <si>
+    <t>error_phone_not_valid</t>
+  </si>
+  <si>
+    <t>Please enter valid phone number</t>
+  </si>
+  <si>
+    <t>error_phone_number_cannot_be_the_same</t>
+  </si>
+  <si>
+    <t>Phone number cannot be the same as your default phone number.</t>
+  </si>
+  <si>
+    <t>error_please_enter_discount_price_ss</t>
+  </si>
+  <si>
+    <t>Please enter discount price</t>
+  </si>
+  <si>
+    <t>error_please_enter_name</t>
+  </si>
+  <si>
+    <t>Please enter name</t>
+  </si>
+  <si>
+    <t>error_please_enter_preparation_time</t>
+  </si>
+  <si>
+    <t>Please enter preparation time</t>
+  </si>
+  <si>
+    <t>error_please_enter_price_ss</t>
+  </si>
+  <si>
+    <t>Please enter price</t>
+  </si>
+  <si>
+    <t>error_please_select_at_least_one_booking_type</t>
+  </si>
+  <si>
+    <t>Please select at least one booking type</t>
+  </si>
+  <si>
+    <t>error_please_select_end_time</t>
+  </si>
+  <si>
+    <t>Please select end time</t>
+  </si>
+  <si>
+    <t>error_please_select_modifier_value_sd</t>
+  </si>
+  <si>
+    <t>Please select {{_VALUE}}</t>
+  </si>
+  <si>
+    <t>error_please_select_start_time</t>
+  </si>
+  <si>
+    <t>Please select start time</t>
+  </si>
+  <si>
+    <t>error_please_select_subscription</t>
+  </si>
+  <si>
+    <t>Please select subscription</t>
+  </si>
+  <si>
+    <t>error_please_select_valid_end_time</t>
+  </si>
+  <si>
+    <t>Please select valid end time</t>
+  </si>
+  <si>
+    <t>error_please_select_valid_timeslot</t>
+  </si>
+  <si>
+    <t>Please select valid timeslot</t>
+  </si>
+  <si>
+    <t>error_select_address_from_your_country</t>
+  </si>
+  <si>
+    <t>Select address from your country</t>
+  </si>
+  <si>
+    <t>error_select_at_least_one_category</t>
+  </si>
+  <si>
+    <t>Please select at least one category</t>
+  </si>
+  <si>
+    <t>error_select_business</t>
+  </si>
+  <si>
+    <t>Please select your business</t>
+  </si>
+  <si>
+    <t>error_service_cart_empty</t>
+  </si>
+  <si>
+    <t>Please add at least one service to your cart before proceeding.</t>
+  </si>
+  <si>
+    <t>error_store_not_provide_delivery_location_sd</t>
+  </si>
+  <si>
+    <t>The store does not provide delivery at your location</t>
+  </si>
+  <si>
+    <t>error_timeslot_already_added</t>
+  </si>
+  <si>
+    <t>Timeslot already added</t>
+  </si>
+  <si>
+    <t>error_you_can_only_select_up_to_options_sd</t>
+  </si>
+  <si>
+    <t>You can only select up to {{_VALUE}} options</t>
+  </si>
+  <si>
+    <t>heading_cart_qd</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>heading_change_merchant_sd</t>
+  </si>
+  <si>
+    <t>Change Merchant?</t>
+  </si>
+  <si>
+    <t>heading_confirmation</t>
+  </si>
+  <si>
+    <t>Confirmation</t>
+  </si>
+  <si>
+    <t>heading_egg</t>
+  </si>
+  <si>
+    <t>Egg</t>
+  </si>
+  <si>
+    <t>heading_main_category</t>
+  </si>
+  <si>
+    <t>Main Category</t>
+  </si>
+  <si>
+    <t>heading_manage_modifier</t>
+  </si>
+  <si>
+    <t>Manage Modifier</t>
+  </si>
+  <si>
+    <t>heading_manage_product</t>
+  </si>
+  <si>
+    <t>Manage Product</t>
+  </si>
+  <si>
+    <t>heading_message_to_your_driver</t>
+  </si>
+  <si>
+    <t>Message to your driver</t>
+  </si>
+  <si>
+    <t>heading_non_veg</t>
+  </si>
+  <si>
+    <t>Non Veg</t>
+  </si>
+  <si>
+    <t>heading_search</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>heading_set_time</t>
+  </si>
+  <si>
+    <t>Set Time</t>
+  </si>
+  <si>
+    <t>heading_veg</t>
+  </si>
+  <si>
+    <t>Veg</t>
+  </si>
+  <si>
+    <t>heading_vegan</t>
+  </si>
+  <si>
+    <t>Vegan</t>
+  </si>
+  <si>
+    <t>hint_address</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>hint_discount_price</t>
+  </si>
+  <si>
+    <t>Discount Price</t>
+  </si>
+  <si>
+    <t>hint_main_category</t>
+  </si>
+  <si>
+    <t>hint_min_order_price</t>
+  </si>
+  <si>
+    <t>hint_preparation_time</t>
+  </si>
+  <si>
+    <t>Preparation Time</t>
+  </si>
+  <si>
+    <t>hint_price</t>
+  </si>
+  <si>
+    <t>Enter price</t>
+  </si>
+  <si>
+    <t>hint_search_from_phone_contact</t>
+  </si>
+  <si>
+    <t>Search from phone contacts</t>
+  </si>
+  <si>
+    <t>hint_search_here</t>
+  </si>
+  <si>
+    <t>Search here...</t>
+  </si>
+  <si>
+    <t>hint_search_main_category</t>
+  </si>
+  <si>
+    <t>Search Main Category</t>
+  </si>
+  <si>
+    <t>hint_select_business</t>
+  </si>
+  <si>
+    <t>hint_write_notes</t>
+  </si>
+  <si>
+    <t>Write notes</t>
+  </si>
+  <si>
+    <t>hint_write_your_ride_experience</t>
+  </si>
+  <si>
+    <t>Write us your experience. We are always happy to hear from you</t>
+  </si>
+  <si>
+    <t>sub_heading_action</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>sub_heading_active</t>
+  </si>
+  <si>
+    <t>sub_heading_active_subscription</t>
+  </si>
+  <si>
+    <t>sub_heading_any</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>sub_heading_cancellation_policy</t>
+  </si>
+  <si>
+    <t>Cancellation Policy</t>
+  </si>
+  <si>
+    <t>sub_heading_discount_price</t>
+  </si>
+  <si>
+    <t>sub_heading_price</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>sub_heading_product</t>
+  </si>
+  <si>
+    <t>sub_heading_subscription</t>
+  </si>
+  <si>
+    <t>sub_heading_type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>sub_heading_update</t>
+  </si>
+  <si>
+    <t>sub_heading_variant</t>
+  </si>
+  <si>
+    <t>Variant</t>
   </si>
 </sst>
 </file>
@@ -868,7 +2248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="10" customWidth="1"/>
@@ -1720,6 +3100,2635 @@
         <v>150</v>
       </c>
     </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>159</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>169</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>187</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>195</v>
+      </c>
+      <c r="B88" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>201</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>203</v>
+      </c>
+      <c r="B92" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>207</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>209</v>
+      </c>
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" t="s">
+        <v>10</v>
+      </c>
+      <c r="C116" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>263</v>
+      </c>
+      <c r="B123" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" t="s">
+        <v>10</v>
+      </c>
+      <c r="C130" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>289</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>291</v>
+      </c>
+      <c r="B137" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>293</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>295</v>
+      </c>
+      <c r="B139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>297</v>
+      </c>
+      <c r="B140" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>299</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>301</v>
+      </c>
+      <c r="B142" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>303</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>305</v>
+      </c>
+      <c r="B144" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>307</v>
+      </c>
+      <c r="B145" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>311</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>313</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>315</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>317</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>319</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>321</v>
+      </c>
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>323</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>325</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>327</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>329</v>
+      </c>
+      <c r="B156" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>331</v>
+      </c>
+      <c r="B157" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>333</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>335</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>337</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>339</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>341</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>343</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>345</v>
+      </c>
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>347</v>
+      </c>
+      <c r="B165" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>349</v>
+      </c>
+      <c r="B166" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>351</v>
+      </c>
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>353</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>355</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>357</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>359</v>
+      </c>
+      <c r="B171" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>361</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>363</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>365</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>367</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>369</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>371</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>373</v>
+      </c>
+      <c r="B178" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>375</v>
+      </c>
+      <c r="B179" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>377</v>
+      </c>
+      <c r="B180" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>378</v>
+      </c>
+      <c r="B181" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>380</v>
+      </c>
+      <c r="B182" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>382</v>
+      </c>
+      <c r="B183" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>384</v>
+      </c>
+      <c r="B184" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>386</v>
+      </c>
+      <c r="B185" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>388</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>390</v>
+      </c>
+      <c r="B187" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>392</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>394</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>395</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>397</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>399</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>401</v>
+      </c>
+      <c r="B193" t="s">
+        <v>10</v>
+      </c>
+      <c r="C193" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>403</v>
+      </c>
+      <c r="B194" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>405</v>
+      </c>
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>407</v>
+      </c>
+      <c r="B196" t="s">
+        <v>10</v>
+      </c>
+      <c r="C196" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>409</v>
+      </c>
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>410</v>
+      </c>
+      <c r="B198" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>412</v>
+      </c>
+      <c r="B199" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>414</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>416</v>
+      </c>
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>418</v>
+      </c>
+      <c r="B202" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>419</v>
+      </c>
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>421</v>
+      </c>
+      <c r="B204" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>423</v>
+      </c>
+      <c r="B205" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>425</v>
+      </c>
+      <c r="B206" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>427</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>429</v>
+      </c>
+      <c r="B208" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>431</v>
+      </c>
+      <c r="B209" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>433</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>435</v>
+      </c>
+      <c r="B211" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>437</v>
+      </c>
+      <c r="B212" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>439</v>
+      </c>
+      <c r="B213" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>441</v>
+      </c>
+      <c r="B214" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>443</v>
+      </c>
+      <c r="B215" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>445</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>447</v>
+      </c>
+      <c r="B217" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>449</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>451</v>
+      </c>
+      <c r="B219" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>453</v>
+      </c>
+      <c r="B220" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>455</v>
+      </c>
+      <c r="B221" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B222" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>459</v>
+      </c>
+      <c r="B223" t="s">
+        <v>10</v>
+      </c>
+      <c r="C223" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>461</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
+      </c>
+      <c r="C224" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>463</v>
+      </c>
+      <c r="B225" t="s">
+        <v>10</v>
+      </c>
+      <c r="C225" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>465</v>
+      </c>
+      <c r="B226" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>467</v>
+      </c>
+      <c r="B227" t="s">
+        <v>10</v>
+      </c>
+      <c r="C227" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>469</v>
+      </c>
+      <c r="B228" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>471</v>
+      </c>
+      <c r="B229" t="s">
+        <v>10</v>
+      </c>
+      <c r="C229" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>472</v>
+      </c>
+      <c r="B230" t="s">
+        <v>10</v>
+      </c>
+      <c r="C230" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>474</v>
+      </c>
+      <c r="B231" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>476</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>478</v>
+      </c>
+      <c r="B233" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>480</v>
+      </c>
+      <c r="B234" t="s">
+        <v>10</v>
+      </c>
+      <c r="C234" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>482</v>
+      </c>
+      <c r="B235" t="s">
+        <v>10</v>
+      </c>
+      <c r="C235" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>484</v>
+      </c>
+      <c r="B236" t="s">
+        <v>10</v>
+      </c>
+      <c r="C236" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>486</v>
+      </c>
+      <c r="B237" t="s">
+        <v>10</v>
+      </c>
+      <c r="C237" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>488</v>
+      </c>
+      <c r="B238" t="s">
+        <v>10</v>
+      </c>
+      <c r="C238" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>490</v>
+      </c>
+      <c r="B239" t="s">
+        <v>10</v>
+      </c>
+      <c r="C239" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>492</v>
+      </c>
+      <c r="B240" t="s">
+        <v>10</v>
+      </c>
+      <c r="C240" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>494</v>
+      </c>
+      <c r="B241" t="s">
+        <v>10</v>
+      </c>
+      <c r="C241" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>496</v>
+      </c>
+      <c r="B242" t="s">
+        <v>10</v>
+      </c>
+      <c r="C242" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>498</v>
+      </c>
+      <c r="B243" t="s">
+        <v>10</v>
+      </c>
+      <c r="C243" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>500</v>
+      </c>
+      <c r="B244" t="s">
+        <v>10</v>
+      </c>
+      <c r="C244" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>502</v>
+      </c>
+      <c r="B245" t="s">
+        <v>10</v>
+      </c>
+      <c r="C245" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>504</v>
+      </c>
+      <c r="B246" t="s">
+        <v>10</v>
+      </c>
+      <c r="C246" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>506</v>
+      </c>
+      <c r="B247" t="s">
+        <v>10</v>
+      </c>
+      <c r="C247" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>508</v>
+      </c>
+      <c r="B248" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>510</v>
+      </c>
+      <c r="B249" t="s">
+        <v>10</v>
+      </c>
+      <c r="C249" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>512</v>
+      </c>
+      <c r="B250" t="s">
+        <v>10</v>
+      </c>
+      <c r="C250" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>514</v>
+      </c>
+      <c r="B251" t="s">
+        <v>10</v>
+      </c>
+      <c r="C251" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>516</v>
+      </c>
+      <c r="B252" t="s">
+        <v>10</v>
+      </c>
+      <c r="C252" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>518</v>
+      </c>
+      <c r="B253" t="s">
+        <v>10</v>
+      </c>
+      <c r="C253" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>520</v>
+      </c>
+      <c r="B254" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>522</v>
+      </c>
+      <c r="B255" t="s">
+        <v>10</v>
+      </c>
+      <c r="C255" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>524</v>
+      </c>
+      <c r="B256" t="s">
+        <v>10</v>
+      </c>
+      <c r="C256" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>526</v>
+      </c>
+      <c r="B257" t="s">
+        <v>10</v>
+      </c>
+      <c r="C257" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>528</v>
+      </c>
+      <c r="B258" t="s">
+        <v>10</v>
+      </c>
+      <c r="C258" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>530</v>
+      </c>
+      <c r="B259" t="s">
+        <v>10</v>
+      </c>
+      <c r="C259" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>532</v>
+      </c>
+      <c r="B260" t="s">
+        <v>10</v>
+      </c>
+      <c r="C260" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>534</v>
+      </c>
+      <c r="B261" t="s">
+        <v>10</v>
+      </c>
+      <c r="C261" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>536</v>
+      </c>
+      <c r="B262" t="s">
+        <v>10</v>
+      </c>
+      <c r="C262" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>538</v>
+      </c>
+      <c r="B263" t="s">
+        <v>10</v>
+      </c>
+      <c r="C263" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>540</v>
+      </c>
+      <c r="B264" t="s">
+        <v>10</v>
+      </c>
+      <c r="C264" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>542</v>
+      </c>
+      <c r="B265" t="s">
+        <v>10</v>
+      </c>
+      <c r="C265" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>544</v>
+      </c>
+      <c r="B266" t="s">
+        <v>10</v>
+      </c>
+      <c r="C266" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>546</v>
+      </c>
+      <c r="B267" t="s">
+        <v>10</v>
+      </c>
+      <c r="C267" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>548</v>
+      </c>
+      <c r="B268" t="s">
+        <v>10</v>
+      </c>
+      <c r="C268" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>550</v>
+      </c>
+      <c r="B269" t="s">
+        <v>10</v>
+      </c>
+      <c r="C269" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>552</v>
+      </c>
+      <c r="B270" t="s">
+        <v>10</v>
+      </c>
+      <c r="C270" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>554</v>
+      </c>
+      <c r="B271" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>556</v>
+      </c>
+      <c r="B272" t="s">
+        <v>10</v>
+      </c>
+      <c r="C272" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>558</v>
+      </c>
+      <c r="B273" t="s">
+        <v>10</v>
+      </c>
+      <c r="C273" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>560</v>
+      </c>
+      <c r="B274" t="s">
+        <v>10</v>
+      </c>
+      <c r="C274" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>562</v>
+      </c>
+      <c r="B275" t="s">
+        <v>10</v>
+      </c>
+      <c r="C275" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>564</v>
+      </c>
+      <c r="B276" t="s">
+        <v>10</v>
+      </c>
+      <c r="C276" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>566</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="C277" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>568</v>
+      </c>
+      <c r="B278" t="s">
+        <v>10</v>
+      </c>
+      <c r="C278" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>570</v>
+      </c>
+      <c r="B279" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>572</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>574</v>
+      </c>
+      <c r="B281" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>576</v>
+      </c>
+      <c r="B282" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>578</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>580</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>582</v>
+      </c>
+      <c r="B285" t="s">
+        <v>10</v>
+      </c>
+      <c r="C285" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>584</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>585</v>
+      </c>
+      <c r="B287" t="s">
+        <v>10</v>
+      </c>
+      <c r="C287" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>586</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>588</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>590</v>
+      </c>
+      <c r="B290" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>592</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="C291" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>594</v>
+      </c>
+      <c r="B292" t="s">
+        <v>10</v>
+      </c>
+      <c r="C292" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>596</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>597</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>599</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>601</v>
+      </c>
+      <c r="B296" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>603</v>
+      </c>
+      <c r="B297" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>604</v>
+      </c>
+      <c r="B298" t="s">
+        <v>10</v>
+      </c>
+      <c r="C298" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>605</v>
+      </c>
+      <c r="B299" t="s">
+        <v>10</v>
+      </c>
+      <c r="C299" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>607</v>
+      </c>
+      <c r="B300" t="s">
+        <v>10</v>
+      </c>
+      <c r="C300" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>609</v>
+      </c>
+      <c r="B301" t="s">
+        <v>10</v>
+      </c>
+      <c r="C301" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>610</v>
+      </c>
+      <c r="B302" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>612</v>
+      </c>
+      <c r="B303" t="s">
+        <v>10</v>
+      </c>
+      <c r="C303" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>613</v>
+      </c>
+      <c r="B304" t="s">
+        <v>10</v>
+      </c>
+      <c r="C304" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>614</v>
+      </c>
+      <c r="B305" t="s">
+        <v>10</v>
+      </c>
+      <c r="C305" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>616</v>
+      </c>
+      <c r="B306" t="s">
+        <v>10</v>
+      </c>
+      <c r="C306" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>617</v>
+      </c>
+      <c r="B307" t="s">
+        <v>10</v>
+      </c>
+      <c r="C307" t="s">
+        <v>618</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
